--- a/Models/Лошади/results/Лошади - Результаты прогнозов SARIMA средние.xlsx
+++ b/Models/Лошади/results/Лошади - Результаты прогнозов SARIMA средние.xlsx
@@ -457,13 +457,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>83.45999999999999</v>
+        <v>78.12</v>
       </c>
       <c r="C2" t="n">
-        <v>67.65000000000001</v>
+        <v>68.16</v>
       </c>
       <c r="D2" t="n">
-        <v>5.15</v>
+        <v>5.08</v>
       </c>
     </row>
     <row r="3">
@@ -473,13 +473,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>174.64</v>
+        <v>211.18</v>
       </c>
       <c r="C3" t="n">
-        <v>146.34</v>
+        <v>169.39</v>
       </c>
       <c r="D3" t="n">
-        <v>7.9</v>
+        <v>7.2</v>
       </c>
     </row>
     <row r="4">
@@ -489,13 +489,13 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>168.18</v>
+        <v>213.67</v>
       </c>
       <c r="C4" t="n">
-        <v>138.81</v>
+        <v>163.33</v>
       </c>
       <c r="D4" t="n">
-        <v>9.07</v>
+        <v>10.08</v>
       </c>
     </row>
     <row r="5">
@@ -505,13 +505,13 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>61.28</v>
+        <v>76.78</v>
       </c>
       <c r="C5" t="n">
-        <v>53.94</v>
+        <v>67.14</v>
       </c>
       <c r="D5" t="n">
-        <v>6.6</v>
+        <v>7.69</v>
       </c>
     </row>
     <row r="6">
@@ -521,13 +521,13 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>327.9</v>
+        <v>275.19</v>
       </c>
       <c r="C6" t="n">
-        <v>274.48</v>
+        <v>218.21</v>
       </c>
       <c r="D6" t="n">
-        <v>18.16</v>
+        <v>12.36</v>
       </c>
     </row>
     <row r="7">
@@ -537,13 +537,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.42</v>
+        <v>0.38</v>
       </c>
       <c r="C7" t="n">
-        <v>0.28</v>
+        <v>0.26</v>
       </c>
       <c r="D7" t="n">
-        <v>3.86610369321697e+18</v>
+        <v>5.961066683118794e+20</v>
       </c>
     </row>
     <row r="8">
@@ -553,13 +553,13 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.76</v>
+        <v>0.85</v>
       </c>
       <c r="C8" t="n">
-        <v>0.68</v>
+        <v>0.7</v>
       </c>
       <c r="D8" t="n">
-        <v>31.94</v>
+        <v>22.23</v>
       </c>
     </row>
     <row r="9">
@@ -569,13 +569,13 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>129.18</v>
+        <v>78.56</v>
       </c>
       <c r="C9" t="n">
-        <v>89.40000000000001</v>
+        <v>64.55</v>
       </c>
       <c r="D9" t="n">
-        <v>76.20999999999999</v>
+        <v>91.95</v>
       </c>
     </row>
     <row r="10">
@@ -585,13 +585,13 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>91.75</v>
+        <v>58</v>
       </c>
       <c r="C10" t="n">
-        <v>76.42</v>
+        <v>50.01</v>
       </c>
       <c r="D10" t="n">
-        <v>5.01</v>
+        <v>3.74</v>
       </c>
     </row>
     <row r="11">
@@ -601,13 +601,13 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>75.54000000000001</v>
+        <v>95.68000000000001</v>
       </c>
       <c r="C11" t="n">
-        <v>61.71</v>
+        <v>69.09999999999999</v>
       </c>
       <c r="D11" t="n">
-        <v>5.51</v>
+        <v>4.89</v>
       </c>
     </row>
     <row r="12">
@@ -617,13 +617,13 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>181.98</v>
+        <v>137.7</v>
       </c>
       <c r="C12" t="n">
-        <v>164.46</v>
+        <v>104.79</v>
       </c>
       <c r="D12" t="n">
-        <v>11.06</v>
+        <v>5.95</v>
       </c>
     </row>
     <row r="13">
@@ -633,13 +633,13 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>82.08</v>
+        <v>49.41</v>
       </c>
       <c r="C13" t="n">
-        <v>70.97</v>
+        <v>43.93</v>
       </c>
       <c r="D13" t="n">
-        <v>15.55</v>
+        <v>9.300000000000001</v>
       </c>
     </row>
     <row r="14">
@@ -649,13 +649,13 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>173.24</v>
+        <v>105.66</v>
       </c>
       <c r="C14" t="n">
-        <v>154.02</v>
+        <v>96.40000000000001</v>
       </c>
       <c r="D14" t="n">
-        <v>18.22</v>
+        <v>12.07</v>
       </c>
     </row>
     <row r="15">
@@ -665,13 +665,13 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>35.26</v>
+        <v>94.64</v>
       </c>
       <c r="C15" t="n">
-        <v>23.38</v>
+        <v>68.51000000000001</v>
       </c>
       <c r="D15" t="n">
-        <v>5.68</v>
+        <v>27.49</v>
       </c>
     </row>
     <row r="16">
@@ -681,13 +681,13 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>940.99</v>
+        <v>619.9</v>
       </c>
       <c r="C16" t="n">
-        <v>789.77</v>
+        <v>462.21</v>
       </c>
       <c r="D16" t="n">
-        <v>30.04</v>
+        <v>13.06</v>
       </c>
     </row>
     <row r="17">
@@ -697,13 +697,13 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>540.98</v>
+        <v>53.85</v>
       </c>
       <c r="C17" t="n">
-        <v>469.27</v>
+        <v>45.61</v>
       </c>
       <c r="D17" t="n">
-        <v>73.38</v>
+        <v>4.11</v>
       </c>
     </row>
     <row r="18">
@@ -713,13 +713,13 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>640.72</v>
+        <v>125.5</v>
       </c>
       <c r="C18" t="n">
-        <v>613.38</v>
+        <v>106.31</v>
       </c>
       <c r="D18" t="n">
-        <v>94.63</v>
+        <v>8.5</v>
       </c>
     </row>
     <row r="19">
@@ -729,13 +729,13 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>945.01</v>
+        <v>635.96</v>
       </c>
       <c r="C19" t="n">
-        <v>751.8200000000001</v>
+        <v>525.4400000000001</v>
       </c>
       <c r="D19" t="n">
-        <v>29.42</v>
+        <v>21.84</v>
       </c>
     </row>
     <row r="20">
@@ -745,13 +745,13 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>35.73</v>
+        <v>38.8</v>
       </c>
       <c r="C20" t="n">
-        <v>32.5</v>
+        <v>31.08</v>
       </c>
       <c r="D20" t="n">
-        <v>5.04</v>
+        <v>4.36</v>
       </c>
     </row>
     <row r="21">
@@ -761,13 +761,13 @@
         </is>
       </c>
       <c r="B21" t="n">
-        <v>625.05</v>
+        <v>617.0700000000001</v>
       </c>
       <c r="C21" t="n">
-        <v>534.6799999999999</v>
+        <v>448.21</v>
       </c>
       <c r="D21" t="n">
-        <v>20.01</v>
+        <v>9.68</v>
       </c>
     </row>
   </sheetData>
